--- a/data/raw/inventory/Week 31/Fossil/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 31/Fossil/Seller FBA Inventory (SP-API).xlsx
@@ -10130,7 +10130,7 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F157" t="n">
         <v>61</v>
@@ -10145,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K157" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L157" t="n">
         <v>2</v>
@@ -10316,7 +10316,7 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F160" t="n">
         <v>16</v>
@@ -10331,10 +10331,10 @@
         <v>0</v>
       </c>
       <c r="J160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K160" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L160" t="n">
         <v>0</v>
@@ -11370,10 +11370,10 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -11385,10 +11385,10 @@
         <v>0</v>
       </c>
       <c r="J177" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K177" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L177" t="n">
         <v>0</v>
@@ -16702,10 +16702,10 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F263" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G263" t="n">
         <v>0</v>
@@ -16717,10 +16717,10 @@
         <v>0</v>
       </c>
       <c r="J263" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K263" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L263" t="n">
         <v>0</v>
@@ -17322,7 +17322,7 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F273" t="n">
         <v>220</v>
@@ -17337,10 +17337,10 @@
         <v>0</v>
       </c>
       <c r="J273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K273" t="n">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L273" t="n">
         <v>3</v>
@@ -18996,7 +18996,7 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F300" t="n">
         <v>2</v>
@@ -19011,10 +19011,10 @@
         <v>0</v>
       </c>
       <c r="J300" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K300" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L300" t="n">
         <v>1</v>

--- a/data/raw/inventory/Week 31/Fossil/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 31/Fossil/Seller FBA Inventory (SP-API).xlsx
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F41" t="n">
         <v>17</v>
@@ -2953,10 +2953,10 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -16702,7 +16702,7 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F263" t="n">
         <v>22</v>
@@ -16717,10 +16717,10 @@
         <v>0</v>
       </c>
       <c r="J263" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K263" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L263" t="n">
         <v>0</v>
@@ -16764,10 +16764,10 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F264" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G264" t="n">
         <v>0</v>
@@ -16779,10 +16779,10 @@
         <v>0</v>
       </c>
       <c r="J264" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K264" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L264" t="n">
         <v>1</v>
@@ -19882,10 +19882,10 @@
         <v>0</v>
       </c>
       <c r="K314" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L314" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M314" t="n">
         <v>0</v>

--- a/data/raw/inventory/Week 31/Fossil/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 31/Fossil/Seller FBA Inventory (SP-API).xlsx
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
@@ -600,7 +600,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -2814,10 +2814,10 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F39" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -2832,10 +2832,10 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="L39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -2879,7 +2879,7 @@
         <v>4</v>
       </c>
       <c r="F40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -2891,7 +2891,7 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
         <v>4</v>
@@ -2941,7 +2941,7 @@
         <v>17</v>
       </c>
       <c r="F41" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -2953,7 +2953,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
         <v>17</v>
@@ -3372,10 +3372,10 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F48" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G48" t="n">
         <v>3</v>
@@ -3390,7 +3390,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -3434,7 +3434,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -3449,10 +3449,10 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L49" t="n">
         <v>1</v>
@@ -3933,7 +3933,7 @@
         <v>5</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57" t="n">
         <v>4</v>
@@ -3945,7 +3945,7 @@
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
         <v>5</v>
@@ -4674,10 +4674,10 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F69" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -4692,7 +4692,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -4860,10 +4860,10 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F72" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G72" t="n">
         <v>8</v>
@@ -4878,7 +4878,7 @@
         <v>1</v>
       </c>
       <c r="K72" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L72" t="n">
         <v>1</v>
@@ -4925,7 +4925,7 @@
         <v>25</v>
       </c>
       <c r="F73" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -4937,7 +4937,7 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K73" t="n">
         <v>25</v>
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F76" t="n">
         <v>20</v>
@@ -5123,10 +5123,10 @@
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
@@ -7092,10 +7092,10 @@
         </is>
       </c>
       <c r="E108" t="n">
+        <v>3</v>
+      </c>
+      <c r="F108" t="n">
         <v>2</v>
-      </c>
-      <c r="F108" t="n">
-        <v>1</v>
       </c>
       <c r="G108" t="n">
         <v>1</v>
@@ -7110,7 +7110,7 @@
         <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
@@ -7712,10 +7712,10 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F118" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -7730,7 +7730,7 @@
         <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
@@ -7963,7 +7963,7 @@
         <v>3</v>
       </c>
       <c r="F122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G122" t="n">
         <v>2</v>
@@ -7975,7 +7975,7 @@
         <v>0</v>
       </c>
       <c r="J122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K122" t="n">
         <v>4</v>
@@ -8149,7 +8149,7 @@
         <v>238</v>
       </c>
       <c r="F125" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -8161,7 +8161,7 @@
         <v>0</v>
       </c>
       <c r="J125" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K125" t="n">
         <v>239</v>
@@ -8208,10 +8208,10 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F126" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G126" t="n">
         <v>3</v>
@@ -8226,7 +8226,7 @@
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L126" t="n">
         <v>1</v>
@@ -9138,10 +9138,10 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -9156,7 +9156,7 @@
         <v>0</v>
       </c>
       <c r="K141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L141" t="n">
         <v>0</v>
@@ -9386,10 +9386,10 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -9404,7 +9404,7 @@
         <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L145" t="n">
         <v>0</v>
@@ -10130,10 +10130,10 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F157" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -10148,7 +10148,7 @@
         <v>0</v>
       </c>
       <c r="K157" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L157" t="n">
         <v>2</v>
@@ -10195,7 +10195,7 @@
         <v>17</v>
       </c>
       <c r="F158" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G158" t="n">
         <v>3</v>
@@ -10207,7 +10207,7 @@
         <v>0</v>
       </c>
       <c r="J158" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K158" t="n">
         <v>17</v>
@@ -14160,7 +14160,7 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F222" t="n">
         <v>8</v>
@@ -14175,10 +14175,10 @@
         <v>0</v>
       </c>
       <c r="J222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K222" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L222" t="n">
         <v>0</v>
@@ -14408,10 +14408,10 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="F226" t="n">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -14426,7 +14426,7 @@
         <v>1</v>
       </c>
       <c r="K226" t="n">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="L226" t="n">
         <v>1</v>
@@ -14470,7 +14470,7 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F227" t="n">
         <v>12</v>
@@ -14485,10 +14485,10 @@
         <v>0</v>
       </c>
       <c r="J227" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K227" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L227" t="n">
         <v>1</v>
@@ -16702,10 +16702,10 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F263" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G263" t="n">
         <v>0</v>
@@ -16720,7 +16720,7 @@
         <v>4</v>
       </c>
       <c r="K263" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L263" t="n">
         <v>0</v>
@@ -16764,10 +16764,10 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F264" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G264" t="n">
         <v>0</v>
@@ -16779,10 +16779,10 @@
         <v>0</v>
       </c>
       <c r="J264" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K264" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="L264" t="n">
         <v>1</v>
@@ -16888,10 +16888,10 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F266" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G266" t="n">
         <v>12</v>
@@ -16906,7 +16906,7 @@
         <v>0</v>
       </c>
       <c r="K266" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L266" t="n">
         <v>0</v>
@@ -17446,10 +17446,10 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F275" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G275" t="n">
         <v>5</v>
@@ -17464,7 +17464,7 @@
         <v>0</v>
       </c>
       <c r="K275" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L275" t="n">
         <v>0</v>
@@ -17880,7 +17880,7 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F282" t="n">
         <v>0</v>
@@ -17895,10 +17895,10 @@
         <v>0</v>
       </c>
       <c r="J282" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K282" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L282" t="n">
         <v>0</v>
@@ -18376,7 +18376,7 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F290" t="n">
         <v>167</v>
@@ -18391,10 +18391,10 @@
         <v>0</v>
       </c>
       <c r="J290" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K290" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L290" t="n">
         <v>1</v>
@@ -18624,10 +18624,10 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="F294" t="n">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="G294" t="n">
         <v>0</v>
@@ -18642,7 +18642,7 @@
         <v>0</v>
       </c>
       <c r="K294" t="n">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="L294" t="n">
         <v>6</v>
@@ -18686,7 +18686,7 @@
         </is>
       </c>
       <c r="E295" t="n">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="F295" t="n">
         <v>593</v>
@@ -18701,10 +18701,10 @@
         <v>0</v>
       </c>
       <c r="J295" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K295" t="n">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="L295" t="n">
         <v>0</v>
@@ -18810,10 +18810,10 @@
         </is>
       </c>
       <c r="E297" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F297" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G297" t="n">
         <v>3</v>
@@ -18825,10 +18825,10 @@
         <v>0</v>
       </c>
       <c r="J297" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K297" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L297" t="n">
         <v>0</v>
@@ -18872,10 +18872,10 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="F298" t="n">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="G298" t="n">
         <v>0</v>
@@ -18887,10 +18887,10 @@
         <v>0</v>
       </c>
       <c r="J298" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K298" t="n">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="L298" t="n">
         <v>1</v>
@@ -18996,7 +18996,7 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F300" t="n">
         <v>2</v>
@@ -19011,10 +19011,10 @@
         <v>0</v>
       </c>
       <c r="J300" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K300" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L300" t="n">
         <v>1</v>
@@ -20177,7 +20177,7 @@
         <v>26</v>
       </c>
       <c r="F319" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G319" t="n">
         <v>3</v>
@@ -20189,7 +20189,7 @@
         <v>0</v>
       </c>
       <c r="J319" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K319" t="n">
         <v>26</v>
@@ -21476,10 +21476,10 @@
         </is>
       </c>
       <c r="E340" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F340" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G340" t="n">
         <v>0</v>
@@ -21494,7 +21494,7 @@
         <v>0</v>
       </c>
       <c r="K340" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L340" t="n">
         <v>0</v>
@@ -21972,7 +21972,7 @@
         </is>
       </c>
       <c r="E348" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F348" t="n">
         <v>5</v>
@@ -21987,10 +21987,10 @@
         <v>0</v>
       </c>
       <c r="J348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K348" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L348" t="n">
         <v>0</v>
@@ -22034,7 +22034,7 @@
         </is>
       </c>
       <c r="E349" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F349" t="n">
         <v>19</v>
@@ -22049,10 +22049,10 @@
         <v>0</v>
       </c>
       <c r="J349" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K349" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L349" t="n">
         <v>0</v>
@@ -23336,7 +23336,7 @@
         </is>
       </c>
       <c r="E370" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F370" t="n">
         <v>4</v>
@@ -23351,10 +23351,10 @@
         <v>0</v>
       </c>
       <c r="J370" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K370" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L370" t="n">
         <v>0</v>
@@ -23401,19 +23401,19 @@
         <v>1</v>
       </c>
       <c r="F371" t="n">
+        <v>0</v>
+      </c>
+      <c r="G371" t="n">
+        <v>0</v>
+      </c>
+      <c r="H371" t="n">
+        <v>0</v>
+      </c>
+      <c r="I371" t="n">
+        <v>0</v>
+      </c>
+      <c r="J371" t="n">
         <v>1</v>
-      </c>
-      <c r="G371" t="n">
-        <v>0</v>
-      </c>
-      <c r="H371" t="n">
-        <v>0</v>
-      </c>
-      <c r="I371" t="n">
-        <v>0</v>
-      </c>
-      <c r="J371" t="n">
-        <v>0</v>
       </c>
       <c r="K371" t="n">
         <v>1</v>
@@ -23711,7 +23711,7 @@
         <v>15</v>
       </c>
       <c r="F376" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G376" t="n">
         <v>0</v>
@@ -23723,7 +23723,7 @@
         <v>0</v>
       </c>
       <c r="J376" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K376" t="n">
         <v>15</v>
@@ -24514,10 +24514,10 @@
         </is>
       </c>
       <c r="E389" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F389" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G389" t="n">
         <v>0</v>
@@ -24532,7 +24532,7 @@
         <v>0</v>
       </c>
       <c r="K389" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L389" t="n">
         <v>0</v>
@@ -24576,10 +24576,10 @@
         </is>
       </c>
       <c r="E390" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F390" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G390" t="n">
         <v>3</v>
@@ -24594,7 +24594,7 @@
         <v>1</v>
       </c>
       <c r="K390" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L390" t="n">
         <v>0</v>
@@ -24638,10 +24638,10 @@
         </is>
       </c>
       <c r="E391" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F391" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G391" t="n">
         <v>6</v>
@@ -24656,7 +24656,7 @@
         <v>0</v>
       </c>
       <c r="K391" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L391" t="n">
         <v>0</v>
@@ -25320,10 +25320,10 @@
         </is>
       </c>
       <c r="E402" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F402" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G402" t="n">
         <v>2</v>
@@ -25335,10 +25335,10 @@
         <v>0</v>
       </c>
       <c r="J402" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K402" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L402" t="n">
         <v>0</v>
@@ -25382,10 +25382,10 @@
         </is>
       </c>
       <c r="E403" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F403" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G403" t="n">
         <v>5</v>
@@ -25397,10 +25397,10 @@
         <v>0</v>
       </c>
       <c r="J403" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K403" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L403" t="n">
         <v>0</v>
@@ -25630,10 +25630,10 @@
         </is>
       </c>
       <c r="E407" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F407" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G407" t="n">
         <v>0</v>
@@ -25648,7 +25648,7 @@
         <v>0</v>
       </c>
       <c r="K407" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L407" t="n">
         <v>0</v>

--- a/data/raw/inventory/Week 31/Fossil/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 31/Fossil/Seller FBA Inventory (SP-API).xlsx
@@ -5049,7 +5049,7 @@
         <v>6</v>
       </c>
       <c r="F75" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -5061,7 +5061,7 @@
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K75" t="n">
         <v>6</v>
@@ -16702,7 +16702,7 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F263" t="n">
         <v>20</v>
@@ -16717,10 +16717,10 @@
         <v>0</v>
       </c>
       <c r="J263" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K263" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L263" t="n">
         <v>0</v>
@@ -16767,7 +16767,7 @@
         <v>47</v>
       </c>
       <c r="F264" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G264" t="n">
         <v>0</v>
@@ -16779,7 +16779,7 @@
         <v>0</v>
       </c>
       <c r="J264" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K264" t="n">
         <v>48</v>
@@ -18627,7 +18627,7 @@
         <v>930</v>
       </c>
       <c r="F294" t="n">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="G294" t="n">
         <v>0</v>
@@ -18639,7 +18639,7 @@
         <v>0</v>
       </c>
       <c r="J294" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K294" t="n">
         <v>936</v>
